--- a/DRIVE.xlsx
+++ b/DRIVE.xlsx
@@ -289,13 +289,7 @@
     <t>Open  brower and enter Google Drive URL</t>
   </si>
   <si>
-    <t>Verify that Google Drive Login/home page should opend.</t>
-  </si>
-  <si>
     <t>Enter valid Gmail ID and Password</t>
-  </si>
-  <si>
-    <t>Verify the User should successfully loged in.</t>
   </si>
   <si>
     <t>Enter valid email and wrong password</t>
@@ -415,9 +409,6 @@
     <t>Right-click file --&gt; file information/details</t>
   </si>
   <si>
-    <t>verify the file details should be displayed.</t>
-  </si>
-  <si>
     <t>Click Google account icon --&gt; Sign out.</t>
   </si>
   <si>
@@ -440,6 +431,15 @@
   </si>
   <si>
     <t>Access to Internet</t>
+  </si>
+  <si>
+    <t>Verify the file details should be displayed.</t>
+  </si>
+  <si>
+    <t>Verify that Google Drive Login/home page should opened.</t>
+  </si>
+  <si>
+    <t>Verify the User should successfully logged in.</t>
   </si>
 </sst>
 </file>
@@ -1225,6 +1225,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF000000"/>
       <color rgb="FFFFF5D1"/>
     </mruColors>
   </colors>
@@ -1237,6 +1238,97 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>253999</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>672288</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1037166</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>1897022</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect l="7521" t="12076"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2878666" y="9530538"/>
+          <a:ext cx="1809750" cy="1224734"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="3175">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>179916</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>476249</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>996119</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>1545564</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2804583" y="3841749"/>
+          <a:ext cx="1842786" cy="1069315"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -28609,14 +28701,14 @@
       </c>
       <c r="B1" s="83"/>
       <c r="C1" s="27" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D1" s="28" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="29"/>
       <c r="F1" s="84" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G1" s="85"/>
       <c r="H1" s="85"/>
@@ -28629,14 +28721,14 @@
       </c>
       <c r="B2" s="78"/>
       <c r="C2" s="31" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D2" s="32" t="s">
         <v>54</v>
       </c>
       <c r="E2" s="33"/>
       <c r="F2" s="81" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G2" s="78"/>
       <c r="H2" s="79" t="s">
@@ -28748,7 +28840,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="81" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C8" s="77"/>
       <c r="D8" s="78"/>
@@ -28794,7 +28886,7 @@
         <v>22</v>
       </c>
       <c r="B11" s="94" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C11" s="95"/>
       <c r="D11" s="95"/>
@@ -28853,7 +28945,7 @@
       </c>
       <c r="J14" s="86"/>
     </row>
-    <row r="15" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="142.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="43">
         <v>1</v>
       </c>
@@ -28862,7 +28954,7 @@
       </c>
       <c r="C15" s="78"/>
       <c r="D15" s="81" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="E15" s="78"/>
       <c r="F15" s="81"/>
@@ -28876,11 +28968,11 @@
         <v>2</v>
       </c>
       <c r="B16" s="81" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C16" s="78"/>
       <c r="D16" s="81" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="E16" s="78"/>
       <c r="F16" s="81"/>
@@ -28894,11 +28986,11 @@
         <v>3</v>
       </c>
       <c r="B17" s="81" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C17" s="78"/>
       <c r="D17" s="81" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E17" s="78"/>
       <c r="F17" s="81"/>
@@ -28912,11 +29004,11 @@
         <v>4</v>
       </c>
       <c r="B18" s="81" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C18" s="78"/>
       <c r="D18" s="81" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E18" s="78"/>
       <c r="F18" s="81"/>
@@ -28930,11 +29022,11 @@
         <v>5</v>
       </c>
       <c r="B19" s="81" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C19" s="78"/>
       <c r="D19" s="81" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E19" s="78"/>
       <c r="F19" s="81"/>
@@ -28948,11 +29040,11 @@
         <v>6</v>
       </c>
       <c r="B20" s="81" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C20" s="78"/>
       <c r="D20" s="81" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E20" s="78"/>
       <c r="F20" s="81"/>
@@ -28966,11 +29058,11 @@
         <v>7</v>
       </c>
       <c r="B21" s="81" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C21" s="78"/>
       <c r="D21" s="81" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E21" s="78"/>
       <c r="F21" s="81"/>
@@ -28984,11 +29076,11 @@
         <v>8</v>
       </c>
       <c r="B22" s="81" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C22" s="78"/>
       <c r="D22" s="81" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E22" s="78"/>
       <c r="F22" s="81"/>
@@ -29016,11 +29108,11 @@
         <v>9</v>
       </c>
       <c r="B24" s="81" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C24" s="78"/>
       <c r="D24" s="81" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E24" s="78"/>
       <c r="F24" s="81"/>
@@ -29029,16 +29121,16 @@
       <c r="I24" s="81"/>
       <c r="J24" s="80"/>
     </row>
-    <row r="25" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" ht="168.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="43">
         <v>10</v>
       </c>
       <c r="B25" s="81" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C25" s="78"/>
       <c r="D25" s="81" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E25" s="78"/>
       <c r="F25" s="81"/>
@@ -29052,11 +29144,11 @@
         <v>11</v>
       </c>
       <c r="B26" s="81" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C26" s="78"/>
       <c r="D26" s="81" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E26" s="78"/>
       <c r="F26" s="81"/>
@@ -29070,11 +29162,11 @@
         <v>12</v>
       </c>
       <c r="B27" s="81" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C27" s="78"/>
       <c r="D27" s="81" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E27" s="78"/>
       <c r="F27" s="81"/>
@@ -29088,11 +29180,11 @@
         <v>13</v>
       </c>
       <c r="B28" s="81" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C28" s="78"/>
       <c r="D28" s="81" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E28" s="78"/>
       <c r="F28" s="97"/>
@@ -29106,11 +29198,11 @@
         <v>14</v>
       </c>
       <c r="B29" s="81" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C29" s="78"/>
       <c r="D29" s="81" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E29" s="77"/>
       <c r="F29" s="100"/>
@@ -29124,11 +29216,11 @@
         <v>15</v>
       </c>
       <c r="B30" s="81" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C30" s="78"/>
       <c r="D30" s="81" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E30" s="77"/>
       <c r="F30" s="100"/>
@@ -29142,11 +29234,11 @@
         <v>16</v>
       </c>
       <c r="B31" s="81" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C31" s="78"/>
       <c r="D31" s="81" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E31" s="77"/>
       <c r="F31" s="100"/>
@@ -29160,11 +29252,11 @@
         <v>17</v>
       </c>
       <c r="B32" s="81" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C32" s="78"/>
       <c r="D32" s="81" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E32" s="77"/>
       <c r="F32" s="100"/>
@@ -29178,11 +29270,11 @@
         <v>18</v>
       </c>
       <c r="B33" s="81" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C33" s="78"/>
       <c r="D33" s="81" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E33" s="77"/>
       <c r="F33" s="100"/>
@@ -29196,11 +29288,11 @@
         <v>19</v>
       </c>
       <c r="B34" s="90" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C34" s="92"/>
       <c r="D34" s="90" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E34" s="91"/>
       <c r="F34" s="100"/>
@@ -29214,11 +29306,11 @@
         <v>20</v>
       </c>
       <c r="B35" s="90" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C35" s="92"/>
       <c r="D35" s="90" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E35" s="92"/>
       <c r="F35" s="103"/>
@@ -29245,11 +29337,11 @@
         <v>21</v>
       </c>
       <c r="B37" s="90" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C37" s="92"/>
       <c r="D37" s="90" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E37" s="92"/>
       <c r="F37" s="103"/>
@@ -29264,11 +29356,11 @@
         <v>22</v>
       </c>
       <c r="B38" s="90" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C38" s="92"/>
       <c r="D38" s="90" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E38" s="92"/>
       <c r="F38" s="103"/>
@@ -29283,11 +29375,11 @@
         <v>23</v>
       </c>
       <c r="B39" s="90" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C39" s="92"/>
       <c r="D39" s="90" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E39" s="92"/>
       <c r="F39" s="103"/>
@@ -29471,5 +29563,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>